--- a/Zinc/5. Statistical data analysis/Plots by site within typology/Sites_by_network_typology.xlsx
+++ b/Zinc/5. Statistical data analysis/Plots by site within typology/Sites_by_network_typology.xlsx
@@ -32,10 +32,10 @@
     <t xml:space="preserve">BSL7</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial Tribs</t>
+    <t xml:space="preserve">NP Tribs (n=1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NP Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">BSL8</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">MCA3.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs (n=5)</t>
+    <t xml:space="preserve">NP Tribs (n=5)</t>
   </si>
   <si>
     <t xml:space="preserve">MCA3.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs (n=4)</t>
+    <t xml:space="preserve">NP Tribs (n=4)</t>
   </si>
   <si>
     <t xml:space="preserve">MTN</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">MTN2</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs (n=2)</t>
+    <t xml:space="preserve">NP Tribs (n=2)</t>
   </si>
   <si>
     <t xml:space="preserve">NBO</t>
@@ -71,34 +71,34 @@
     <t xml:space="preserve">NBO3</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs (n=4); Perennial Tribs (n=2)</t>
+    <t xml:space="preserve">NP Tribs (n=4); P Tribs (n=2)</t>
   </si>
   <si>
     <t xml:space="preserve">BSL4.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs (n=4); Main Stem (n=2); Perennial Developed Tribs (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial Tribs</t>
+    <t xml:space="preserve">P Tribs (n=4); Main Stem (n=2); PD Tribs (n=1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">BSL4.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs (n=4)</t>
+    <t xml:space="preserve">P Tribs (n=4)</t>
   </si>
   <si>
     <t xml:space="preserve">BSL4.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs (n=3); Main Stem (n=1)</t>
+    <t xml:space="preserve">P Tribs (n=3); Main Stem (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">BSL5.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs (n=1)</t>
+    <t xml:space="preserve">P Tribs (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">BSL6</t>
@@ -107,31 +107,31 @@
     <t xml:space="preserve">MCA2</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs (n=3)</t>
+    <t xml:space="preserve">P Tribs (n=3)</t>
   </si>
   <si>
     <t xml:space="preserve">MCA3.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs (n=5); Perennial Developed Tribs (n=4)</t>
+    <t xml:space="preserve">P Tribs (n=5); PD Tribs (n=4)</t>
   </si>
   <si>
     <t xml:space="preserve">MCA4</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs (n=8); Perennial Developed Tribs (n=3)</t>
+    <t xml:space="preserve">P Tribs (n=8); PD Tribs (n=3)</t>
   </si>
   <si>
     <t xml:space="preserve">MTN4</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs (n=5); Perennial Developed Tribs (n=5); Non-Perennial Tribs (n=1)</t>
+    <t xml:space="preserve">P Tribs (n=5); PD Tribs (n=5); NP Tribs (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">NBO5</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs (n=6)</t>
+    <t xml:space="preserve">P Tribs (n=6)</t>
   </si>
   <si>
     <t xml:space="preserve">S_TRIB</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">Gum Hollow</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs (n=11)</t>
+    <t xml:space="preserve">P Tribs (n=11)</t>
   </si>
   <si>
     <t xml:space="preserve">Mill Branch</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">Pinhook Branch</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs (n=10)</t>
+    <t xml:space="preserve">P Tribs (n=10)</t>
   </si>
   <si>
     <t xml:space="preserve">WBK</t>
@@ -158,52 +158,52 @@
     <t xml:space="preserve">WBK2</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs (n=2); Main Stem (n=2); Non-Perennial Tribs (n=1)</t>
+    <t xml:space="preserve">P Tribs (n=2); Main Stem (n=2); NP Tribs (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">WBK3</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs (n=8)</t>
+    <t xml:space="preserve">P Tribs (n=8)</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Developed Tribs (n=8); Main Stem (n=2); Perennial Tribs (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial Developed Tribs</t>
+    <t xml:space="preserve">PD Tribs (n=8); Main Stem (n=2); P Tribs (n=1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Developed Tribs (n=9); Perennial Tribs (n=1); Main Stem (n=1)</t>
+    <t xml:space="preserve">PD Tribs (n=9); P Tribs (n=1); Main Stem (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">BSL2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Developed Tribs (n=10)</t>
+    <t xml:space="preserve">PD Tribs (n=10)</t>
   </si>
   <si>
     <t xml:space="preserve">BSL2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Developed Tribs (n=6); Perennial Tribs (n=2); Main Stem (n=2)</t>
+    <t xml:space="preserve">PD Tribs (n=6); P Tribs (n=2); Main Stem (n=2)</t>
   </si>
   <si>
     <t xml:space="preserve">BSL2.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Developed Tribs (n=9); Perennial Tribs (n=1)</t>
+    <t xml:space="preserve">PD Tribs (n=9); P Tribs (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">BSL3.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Developed Tribs (n=10); Perennial Tribs (n=1)</t>
+    <t xml:space="preserve">PD Tribs (n=10); P Tribs (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">BSL3.2</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">Downtown</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Developed Tribs (n=5); Main Stem (n=3); Perennial Tribs (n=1)</t>
+    <t xml:space="preserve">PD Tribs (n=5); Main Stem (n=3); P Tribs (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">MCA1</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Developed Tribs (n=8); Perennial Tribs (n=3)</t>
+    <t xml:space="preserve">PD Tribs (n=8); P Tribs (n=3)</t>
   </si>
   <si>
     <t xml:space="preserve">MTN1.1</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">WBK1</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Developed Tribs (n=11); Perennial Tribs (n=1)</t>
+    <t xml:space="preserve">PD Tribs (n=11); P Tribs (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Main Stem (n=10); Perennial Tribs (n=1)</t>
+    <t xml:space="preserve">Main Stem (n=10); P Tribs (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">Main Stem</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">EFK18.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Main Stem (n=9); Perennial Tribs (n=1)</t>
+    <t xml:space="preserve">Main Stem (n=9); P Tribs (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">EFK2.0</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">EFK7.9</t>
   </si>
   <si>
-    <t xml:space="preserve">Main Stem (n=8); Perennial Tribs (n=1)</t>
+    <t xml:space="preserve">Main Stem (n=8); P Tribs (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">BCK0.9</t>

--- a/Zinc/5. Statistical data analysis/Plots by site within typology/Sites_by_network_typology.xlsx
+++ b/Zinc/5. Statistical data analysis/Plots by site within typology/Sites_by_network_typology.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t xml:space="preserve">Network</t>
   </si>
@@ -26,114 +26,90 @@
     <t xml:space="preserve">Dominant_Typology</t>
   </si>
   <si>
+    <t xml:space="preserve">MCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NP Tribs (n=4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NP Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NP Tribs (n=4); P Tribs (n=2)</t>
+  </si>
+  <si>
     <t xml:space="preserve">BSL</t>
   </si>
   <si>
-    <t xml:space="preserve">BSL7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NP Tribs (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NP Tribs</t>
+    <t xml:space="preserve">BSL4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P Tribs (n=2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P Tribs (n=1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL5.1</t>
   </si>
   <si>
     <t xml:space="preserve">BSL8</t>
   </si>
   <si>
-    <t xml:space="preserve">MCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NP Tribs (n=5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NP Tribs (n=4)</t>
+    <t xml:space="preserve">MCA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P Tribs (n=3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P Tribs (n=5); PD Tribs (n=3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P Tribs (n=8); PD Tribs (n=3)</t>
   </si>
   <si>
     <t xml:space="preserve">MTN</t>
   </si>
   <si>
-    <t xml:space="preserve">MTN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NP Tribs (n=2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NP Tribs (n=4); P Tribs (n=2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P Tribs (n=4); Main Stem (n=2); PD Tribs (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL4.2</t>
+    <t xml:space="preserve">MTN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P Tribs (n=5); PD Tribs (n=5); NP Tribs (n=1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBO5</t>
   </si>
   <si>
     <t xml:space="preserve">P Tribs (n=4)</t>
   </si>
   <si>
-    <t xml:space="preserve">BSL4.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P Tribs (n=3); Main Stem (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL5.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P Tribs (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P Tribs (n=3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P Tribs (n=5); PD Tribs (n=4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P Tribs (n=8); PD Tribs (n=3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P Tribs (n=5); PD Tribs (n=5); NP Tribs (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBO5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P Tribs (n=6)</t>
-  </si>
-  <si>
     <t xml:space="preserve">S_TRIB</t>
   </si>
   <si>
@@ -158,13 +134,13 @@
     <t xml:space="preserve">WBK2</t>
   </si>
   <si>
-    <t xml:space="preserve">P Tribs (n=2); Main Stem (n=2); NP Tribs (n=1)</t>
+    <t xml:space="preserve">P Tribs (n=2); NP Tribs (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">WBK3</t>
   </si>
   <si>
-    <t xml:space="preserve">P Tribs (n=8)</t>
+    <t xml:space="preserve">P Tribs (n=7)</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.1</t>
@@ -191,7 +167,7 @@
     <t xml:space="preserve">BSL2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">PD Tribs (n=6); P Tribs (n=2); Main Stem (n=2)</t>
+    <t xml:space="preserve">PD Tribs (n=7); Main Stem (n=2); P Tribs (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">BSL2.3</t>
@@ -225,6 +201,9 @@
   </si>
   <si>
     <t xml:space="preserve">MTN1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD Tribs (n=2)</t>
   </si>
   <si>
     <t xml:space="preserve">NBO2</t>
@@ -674,72 +653,72 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -747,13 +726,13 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -761,13 +740,13 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -775,27 +754,27 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -803,209 +782,209 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
         <v>34</v>
       </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
         <v>40</v>
       </c>
-      <c r="B18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" t="s">
-        <v>42</v>
-      </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
         <v>42</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
         <v>44</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>45</v>
-      </c>
-      <c r="D20" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
         <v>46</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>47</v>
       </c>
-      <c r="C21" t="s">
-        <v>48</v>
-      </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s">
         <v>49</v>
       </c>
-      <c r="C22" t="s">
-        <v>50</v>
-      </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" t="s">
         <v>51</v>
       </c>
-      <c r="C23" t="s">
-        <v>52</v>
-      </c>
       <c r="D23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D28" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
@@ -1013,265 +992,223 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D29" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D32" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="B34" t="s">
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s">
         <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D35" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D36" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D37" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" t="s">
         <v>77</v>
       </c>
-      <c r="B39" t="s">
-        <v>80</v>
-      </c>
       <c r="C39" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D40" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C41" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D41" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C42" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D42" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C43" t="s">
         <v>83</v>
       </c>
       <c r="D43" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D44" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>77</v>
-      </c>
-      <c r="B45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>77</v>
-      </c>
-      <c r="B46" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" t="s">
-        <v>90</v>
-      </c>
-      <c r="D46" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Zinc/5. Statistical data analysis/Plots by site within typology/Sites_by_network_typology.xlsx
+++ b/Zinc/5. Statistical data analysis/Plots by site within typology/Sites_by_network_typology.xlsx
@@ -26,6 +26,66 @@
     <t xml:space="preserve">Dominant_Typology</t>
   </si>
   <si>
+    <t xml:space="preserve">BSL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem (n=10); P Tribs (n=1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK10.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK11.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK13.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK16.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK18.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem (n=9); P Tribs (n=1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK23.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem (n=11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK5.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK7.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem (n=8); P Tribs (n=1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S_TRIB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCK0.9</t>
+  </si>
+  <si>
     <t xml:space="preserve">MCA</t>
   </si>
   <si>
@@ -50,9 +110,6 @@
     <t xml:space="preserve">NP Tribs (n=4); P Tribs (n=2)</t>
   </si>
   <si>
-    <t xml:space="preserve">BSL</t>
-  </si>
-  <si>
     <t xml:space="preserve">BSL4.1</t>
   </si>
   <si>
@@ -110,9 +167,6 @@
     <t xml:space="preserve">P Tribs (n=4)</t>
   </si>
   <si>
-    <t xml:space="preserve">S_TRIB</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gum Hollow</t>
   </si>
   <si>
@@ -155,7 +209,7 @@
     <t xml:space="preserve">BSL1.3</t>
   </si>
   <si>
-    <t xml:space="preserve">PD Tribs (n=9); P Tribs (n=1); Main Stem (n=1)</t>
+    <t xml:space="preserve">PD Tribs (n=9); Main Stem (n=1); P Tribs (n=1)</t>
   </si>
   <si>
     <t xml:space="preserve">BSL2.1</t>
@@ -213,60 +267,6 @@
   </si>
   <si>
     <t xml:space="preserve">PD Tribs (n=11); P Tribs (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem (n=10); P Tribs (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK10.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK11.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK13.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK16.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK18.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem (n=9); P Tribs (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK2.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK23.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem (n=11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK5.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK7.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem (n=8); P Tribs (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCK0.9</t>
   </si>
 </sst>
 </file>
@@ -625,10 +625,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -639,13 +639,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -653,562 +653,562 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D34" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
         <v>70</v>
       </c>
-      <c r="B36" t="s">
-        <v>73</v>
-      </c>
       <c r="C36" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D36" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D37" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D38" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C39" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D39" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D40" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="B41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" t="s">
         <v>79</v>
       </c>
-      <c r="C41" t="s">
-        <v>80</v>
-      </c>
       <c r="D41" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" t="s">
         <v>81</v>
       </c>
-      <c r="C42" t="s">
-        <v>68</v>
-      </c>
       <c r="D42" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
         <v>82</v>
       </c>
       <c r="C43" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="D43" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="B44" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" t="s">
         <v>84</v>
       </c>
-      <c r="C44" t="s">
-        <v>68</v>
-      </c>
       <c r="D44" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
